--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$86</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="307">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -796,73 +796,36 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>Organizer.component:frNaissance</t>
-  </si>
-  <si>
-    <t>frNaissance</t>
-  </si>
-  <si>
-    <t>Organizer.component:frNaissance.nullFlavor</t>
+    <t>Naissance (organizer) ou observation sur la grossesse (observation)</t>
   </si>
   <si>
     <t>Organizer.component.nullFlavor</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.realmCode</t>
-  </si>
-  <si>
     <t>Organizer.component.realmCode</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.typeId</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.typeId.nullFlavor</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.nullFlavor</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.assigningAuthorityName</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.typeId.displayable</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.displayable</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.typeId.root</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.root</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.typeId.extension</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.extension</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.templateId</t>
-  </si>
-  <si>
     <t>Organizer.component.templateId</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.typeCode</t>
-  </si>
-  <si>
     <t>Organizer.component.typeCode</t>
   </si>
   <si>
@@ -875,9 +838,6 @@
     <t>OrganizerComponent.typeCode</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.contextConductionInd</t>
-  </si>
-  <si>
     <t>Organizer.component.contextConductionInd</t>
   </si>
   <si>
@@ -885,9 +845,6 @@
   </si>
   <si>
     <t>OrganizerComponent.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Organizer.component:frNaissance.sequenceNumber</t>
   </si>
   <si>
     <t>Organizer.component.sequenceNumber</t>
@@ -900,16 +857,10 @@
     <t>OrganizerComponent.sequenceNumber</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.sdtcPriorityNumber</t>
-  </si>
-  <si>
     <t>Organizer.component.sdtcPriorityNumber</t>
   </si>
   <si>
     <t>OrganizerComponent.sdtcPriorityNumber</t>
-  </si>
-  <si>
-    <t>Organizer.component:frNaissance.seperatableInd</t>
   </si>
   <si>
     <t>Organizer.component.seperatableInd</t>
@@ -922,9 +873,6 @@
     <t>OrganizerComponent.seperatableInd</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.act</t>
-  </si>
-  <si>
     <t>Organizer.component.act</t>
   </si>
   <si>
@@ -935,9 +883,6 @@
     <t>OrganizerComponent.act</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.encounter</t>
-  </si>
-  <si>
     <t>Organizer.component.encounter</t>
   </si>
   <si>
@@ -948,9 +893,6 @@
     <t>OrganizerComponent.encounter</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.observation</t>
-  </si>
-  <si>
     <t>Organizer.component.observation</t>
   </si>
   <si>
@@ -967,9 +909,6 @@
     <t>OrganizerComponent.observation</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.observationMedia</t>
-  </si>
-  <si>
     <t>Organizer.component.observationMedia</t>
   </si>
   <si>
@@ -980,9 +919,6 @@
     <t>OrganizerComponent.observationMedia</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.organizer</t>
-  </si>
-  <si>
     <t>Organizer.component.organizer</t>
   </si>
   <si>
@@ -999,9 +935,6 @@
     <t>OrganizerComponent.organizer</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.procedure</t>
-  </si>
-  <si>
     <t>Organizer.component.procedure</t>
   </si>
   <si>
@@ -1012,9 +945,6 @@
     <t>OrganizerComponent.procedure</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.regionOfInterest</t>
-  </si>
-  <si>
     <t>Organizer.component.regionOfInterest</t>
   </si>
   <si>
@@ -1025,9 +955,6 @@
     <t>OrganizerComponent.regionOfInterest</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.substanceAdministration</t>
-  </si>
-  <si>
     <t>Organizer.component.substanceAdministration</t>
   </si>
   <si>
@@ -1038,9 +965,6 @@
     <t>OrganizerComponent.substanceAdministration</t>
   </si>
   <si>
-    <t>Organizer.component:frNaissance.supply</t>
-  </si>
-  <si>
     <t>Organizer.component.supply</t>
   </si>
   <si>
@@ -1049,12 +973,6 @@
   </si>
   <si>
     <t>OrganizerComponent.supply</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationSurLaGrossesse</t>
-  </si>
-  <si>
-    <t>frObservationSurLaGrossesse</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK88"/>
+  <dimension ref="A1:AK86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.0859375" customWidth="true" bestFit="true"/>
@@ -7724,7 +7642,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>249</v>
       </c>
@@ -7754,7 +7672,9 @@
       <c r="K63" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L63" s="2"/>
+      <c r="L63" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7793,14 +7713,16 @@
         <v>75</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>249</v>
@@ -7826,15 +7748,15 @@
         <v>252</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E64" s="2"/>
+      <c r="E64" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F64" t="s" s="2">
         <v>81</v>
       </c>
@@ -7851,10 +7773,12 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>250</v>
+        <v>86</v>
       </c>
       <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
+      <c r="M64" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -7880,13 +7804,11 @@
         <v>75</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>75</v>
@@ -7904,13 +7826,13 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>75</v>
@@ -7924,23 +7846,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E65" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>75</v>
@@ -7952,11 +7872,11 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7983,11 +7903,13 @@
         <v>75</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>75</v>
@@ -8005,13 +7927,13 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>75</v>
@@ -8025,10 +7947,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8039,7 +7961,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>75</v>
@@ -8051,11 +7973,11 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8106,19 +8028,19 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
@@ -8126,16 +8048,18 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E67" s="2"/>
+      <c r="E67" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F67" t="s" s="2">
         <v>81</v>
       </c>
@@ -8152,11 +8076,11 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8183,13 +8107,11 @@
         <v>75</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>75</v>
@@ -8207,7 +8129,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8219,7 +8141,7 @@
         <v>75</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>75</v>
@@ -8227,17 +8149,17 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>81</v>
@@ -8255,11 +8177,11 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8286,11 +8208,13 @@
         <v>75</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>75</v>
@@ -8308,7 +8232,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -8328,17 +8252,17 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>81</v>
@@ -8356,11 +8280,11 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8411,7 +8335,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -8431,20 +8355,20 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F70" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>76</v>
@@ -8459,11 +8383,11 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8472,7 +8396,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>75</v>
@@ -8514,7 +8438,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -8534,17 +8458,17 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>76</v>
@@ -8562,11 +8486,11 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8575,7 +8499,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>75</v>
@@ -8617,7 +8541,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -8637,23 +8561,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E72" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>75</v>
@@ -8665,11 +8587,11 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8720,13 +8642,13 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>75</v>
@@ -8740,10 +8662,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8754,7 +8676,7 @@
         <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>75</v>
@@ -8766,23 +8688,21 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L73" s="2"/>
-      <c r="M73" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
-        <v>75</v>
+        <v>262</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>75</v>
+        <v>262</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>75</v>
@@ -8797,13 +8717,11 @@
         <v>75</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>75</v>
+        <v>263</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -8821,13 +8739,13 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>126</v>
+        <v>264</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>75</v>
@@ -8841,10 +8759,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8867,21 +8785,21 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
-        <v>274</v>
+        <v>75</v>
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>274</v>
+        <v>75</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>75</v>
@@ -8896,11 +8814,13 @@
         <v>75</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>275</v>
+        <v>75</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>75</v>
@@ -8918,7 +8838,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -8938,10 +8858,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8964,7 +8884,7 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>108</v>
+        <v>269</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -8975,7 +8895,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>279</v>
+        <v>75</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>75</v>
@@ -9017,7 +8937,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -9037,10 +8957,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9063,7 +8983,7 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9116,7 +9036,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -9136,10 +9056,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9162,7 +9082,7 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9215,7 +9135,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -9235,10 +9155,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9261,7 +9181,7 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9314,7 +9234,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -9334,10 +9254,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9360,7 +9280,7 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9413,7 +9333,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9433,10 +9353,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9459,10 +9379,14 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9512,7 +9436,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -9532,10 +9456,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9558,14 +9482,10 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -9615,7 +9535,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -9635,10 +9555,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9661,10 +9581,14 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -9714,7 +9638,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -9734,10 +9658,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9760,14 +9684,10 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="L83" s="2"/>
+      <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -9817,7 +9737,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -9837,10 +9757,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9863,7 +9783,7 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -9916,7 +9836,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -9936,10 +9856,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9962,7 +9882,7 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10015,7 +9935,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -10035,10 +9955,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10061,7 +9981,7 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10114,7 +10034,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -10132,208 +10052,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="D88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK88">
+  <autoFilter ref="A1:AK86">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10343,7 +10063,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI87">
+  <conditionalFormatting sqref="A2:AI85">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
